--- a/content/xls/NSO_f_regions_01.01.2026.xlsx
+++ b/content/xls/NSO_f_regions_01.01.2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\Новое\13.08\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E561CD7-85B2-4D0A-8AAC-32621D177AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C824EF-6BC2-4806-AA08-24E9BF4C2479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="12283" yWindow="1822" windowWidth="25317" windowHeight="14104" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,6 @@
     <t>Болотнинский муниципальный район</t>
   </si>
   <si>
-    <t>Венгеровский муниципальный район</t>
-  </si>
-  <si>
-    <t>Доволенский муниципальный район</t>
-  </si>
-  <si>
     <t>Здвинский муниципальный район</t>
   </si>
   <si>
@@ -87,27 +81,15 @@
     <t>Ордынский муниципальный район</t>
   </si>
   <si>
-    <t>Северный муниципальный район</t>
-  </si>
-  <si>
-    <t>Сузунский муниципальный район</t>
-  </si>
-  <si>
     <t>Татарский муниципальный округ</t>
   </si>
   <si>
     <t>Тогучинский муниципальный район</t>
   </si>
   <si>
-    <t>Убинский муниципальный район</t>
-  </si>
-  <si>
     <t>Усть-Таркский муниципальный район</t>
   </si>
   <si>
-    <t>Чановский муниципальный район</t>
-  </si>
-  <si>
     <t>Черепановский муниципальный район</t>
   </si>
   <si>
@@ -151,6 +133,24 @@
   </si>
   <si>
     <t>Муниципальное образование</t>
+  </si>
+  <si>
+    <t>Венгеровский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Доволенский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Северный муниципальный округ</t>
+  </si>
+  <si>
+    <t>Сузунский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Убинский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Чановский муниципальный округ</t>
   </si>
 </sst>
 </file>
@@ -646,40 +646,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="5" customFormat="1" ht="91.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -798,7 +798,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1">
         <v>14630</v>
@@ -836,7 +836,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B6" s="1">
         <v>12574</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1">
         <v>11776</v>
@@ -912,7 +912,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>57989</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1">
         <v>13325</v>
@@ -988,7 +988,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>5291</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>24203</v>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1">
         <v>44354</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1">
         <v>11524</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1">
         <v>27615</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1">
         <v>11205</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1">
         <v>10013</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1">
         <v>8395</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1">
         <v>23573</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B19" s="1">
         <v>40472</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1">
         <v>160478</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1">
         <v>33533</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1">
         <v>7258</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1">
         <v>31325</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1">
         <v>12496</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B25" s="1">
         <v>32597</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1">
         <v>10716</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B27" s="1">
         <v>10216</v>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1">
         <v>20330</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1">
         <v>29097</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B30" s="1">
         <v>13816</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1">
         <v>7668</v>

--- a/content/xls/NSO_f_regions_01.01.2026.xlsx
+++ b/content/xls/NSO_f_regions_01.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C824EF-6BC2-4806-AA08-24E9BF4C2479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654B5618-67CB-4281-B708-3D421ECF55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12283" yWindow="1822" windowWidth="25317" windowHeight="14104" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
